--- a/Result/profitability/5902.xlsx
+++ b/Result/profitability/5902.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.19</v>
       </c>
       <c r="M2" t="n">
-        <v>0.42875</v>
+        <v>0.43125</v>
       </c>
       <c r="N2" t="n">
-        <v>24.79375</v>
+        <v>25.02625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.17</v>
       </c>
       <c r="M3" t="n">
-        <v>0.335</v>
+        <v>0.3675</v>
       </c>
       <c r="N3" t="n">
-        <v>25.815</v>
+        <v>26.545</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.89</v>
       </c>
       <c r="M4" t="n">
-        <v>0.18125</v>
+        <v>0.18875</v>
       </c>
       <c r="N4" t="n">
-        <v>18.085</v>
+        <v>18.5075</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-4.38</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.43375</v>
+        <v>-0.44125</v>
       </c>
       <c r="N5" t="n">
-        <v>15.7225</v>
+        <v>16.05375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.53125</v>
+        <v>-0.53</v>
       </c>
       <c r="N6" t="n">
-        <v>15.35</v>
+        <v>15.4575</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.16</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.625</v>
+        <v>-0.60625</v>
       </c>
       <c r="N7" t="n">
-        <v>15.28</v>
+        <v>15.56</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.39</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.73</v>
+        <v>-0.7125</v>
       </c>
       <c r="N8" t="n">
-        <v>15.05375</v>
+        <v>15.29625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5902</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>570</v>
+      </c>
+      <c r="D75" t="n">
+        <v>420</v>
+      </c>
+      <c r="E75" t="n">
+        <v>150</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.26</v>
+      </c>
+      <c r="G75" t="n">
+        <v>70</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>12.27%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>73</v>
+      </c>
+      <c r="K75" t="n">
+        <v>56</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.5275</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.91375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3043478260869563</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.940000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.07976973684210531</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.06000000000000005</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.09090909090909094</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.650000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1122405760271072</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
